--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6257-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6257-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFEB2982-F02E-482E-9C00-7A47BFC9FF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BB0A1D6-BEE2-4A43-BBCF-7BDD9218F0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{28C2B87D-BD10-4B9D-B9F2-77104826493A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{097DE4EC-6800-4EE0-9DE3-9DFA34D3496C}"/>
   </bookViews>
   <sheets>
     <sheet name="6257-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1511,26 +1511,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76055E88-E944-4507-A720-52C681FE8B37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516B01B0-9C9C-4DAD-B8D9-7C67B230E11A}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1600,7 +1600,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1720,7 +1720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>33</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>33</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>33</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2019</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>33</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>33</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2018</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2017</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2016</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2015</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2014</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2013</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2012</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2011</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2010</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2009</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2008</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2007</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2006</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2005</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2004</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2003</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2002</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2001</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2000</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37" t="s">
         <v>58</v>
       </c>
